--- a/AI使用记录.xlsx
+++ b/AI使用记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\testdemo\java-demo\fastApi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834FE46D-23B8-4A9A-8677-CE7758F128D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23C2293-BD04-4A42-B9D6-993C382B2C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1、项目起步过程" sheetId="2" r:id="rId1"/>
@@ -204,7 +204,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -219,6 +219,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -238,13 +244,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1105,15 +1112,15 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:8" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1128,25 +1135,25 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:6" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="61" spans="2:9" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1157,181 +1164,415 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:AD63"/>
+  <dimension ref="B2:AK63"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:30" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="2:37" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD3" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD3" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD4" s="1"/>
-    </row>
-    <row r="5" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD5" s="1" t="s">
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="6"/>
+      <c r="AJ3" s="6"/>
+      <c r="AK3" s="6"/>
+    </row>
+    <row r="4" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="6"/>
+    </row>
+    <row r="5" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD5" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD6" s="1" t="s">
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6"/>
+      <c r="AG5" s="6"/>
+      <c r="AH5" s="6"/>
+      <c r="AI5" s="6"/>
+      <c r="AJ5" s="6"/>
+      <c r="AK5" s="6"/>
+    </row>
+    <row r="6" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD6" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD7" s="1" t="s">
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="6"/>
+      <c r="AG6" s="6"/>
+      <c r="AH6" s="6"/>
+      <c r="AI6" s="6"/>
+      <c r="AJ6" s="6"/>
+      <c r="AK6" s="6"/>
+    </row>
+    <row r="7" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD7" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD8" s="1" t="s">
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="6"/>
+      <c r="AI7" s="6"/>
+      <c r="AJ7" s="6"/>
+      <c r="AK7" s="6"/>
+    </row>
+    <row r="8" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD8" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD9" s="1" t="s">
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="6"/>
+      <c r="AG8" s="6"/>
+      <c r="AH8" s="6"/>
+      <c r="AI8" s="6"/>
+      <c r="AJ8" s="6"/>
+      <c r="AK8" s="6"/>
+    </row>
+    <row r="9" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD9" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD10" s="1" t="s">
+      <c r="AE9" s="6"/>
+      <c r="AF9" s="6"/>
+      <c r="AG9" s="6"/>
+      <c r="AH9" s="6"/>
+      <c r="AI9" s="6"/>
+      <c r="AJ9" s="6"/>
+      <c r="AK9" s="6"/>
+    </row>
+    <row r="10" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD10" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD11" s="1" t="s">
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="6"/>
+      <c r="AJ10" s="6"/>
+      <c r="AK10" s="6"/>
+    </row>
+    <row r="11" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD11" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD12" s="1" t="s">
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="6"/>
+      <c r="AI11" s="6"/>
+      <c r="AJ11" s="6"/>
+      <c r="AK11" s="6"/>
+    </row>
+    <row r="12" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD12" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD13" s="1" t="s">
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6"/>
+      <c r="AI12" s="6"/>
+      <c r="AJ12" s="6"/>
+      <c r="AK12" s="6"/>
+    </row>
+    <row r="13" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD13" s="5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="14" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD14" s="1" t="s">
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="6"/>
+      <c r="AI13" s="6"/>
+      <c r="AJ13" s="6"/>
+      <c r="AK13" s="6"/>
+    </row>
+    <row r="14" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD14" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD15" s="1" t="s">
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="6"/>
+    </row>
+    <row r="15" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD15" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="16" spans="2:30" x14ac:dyDescent="0.2">
-      <c r="AD16" s="1" t="s">
+      <c r="AE15" s="6"/>
+      <c r="AF15" s="6"/>
+      <c r="AG15" s="6"/>
+      <c r="AH15" s="6"/>
+      <c r="AI15" s="6"/>
+      <c r="AJ15" s="6"/>
+      <c r="AK15" s="6"/>
+    </row>
+    <row r="16" spans="2:37" x14ac:dyDescent="0.2">
+      <c r="AD16" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD17" s="1" t="s">
+      <c r="AE16" s="6"/>
+      <c r="AF16" s="6"/>
+      <c r="AG16" s="6"/>
+      <c r="AH16" s="6"/>
+      <c r="AI16" s="6"/>
+      <c r="AJ16" s="6"/>
+      <c r="AK16" s="6"/>
+    </row>
+    <row r="17" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD17" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD18" s="1"/>
-    </row>
-    <row r="19" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD19" s="1" t="s">
+      <c r="AE17" s="6"/>
+      <c r="AF17" s="6"/>
+      <c r="AG17" s="6"/>
+      <c r="AH17" s="6"/>
+      <c r="AI17" s="6"/>
+      <c r="AJ17" s="6"/>
+      <c r="AK17" s="6"/>
+    </row>
+    <row r="18" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="6"/>
+      <c r="AJ18" s="6"/>
+      <c r="AK18" s="6"/>
+    </row>
+    <row r="19" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD19" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD20" s="1"/>
-    </row>
-    <row r="21" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD21" s="1" t="s">
+      <c r="AE19" s="6"/>
+      <c r="AF19" s="6"/>
+      <c r="AG19" s="6"/>
+      <c r="AH19" s="6"/>
+      <c r="AI19" s="6"/>
+      <c r="AJ19" s="6"/>
+      <c r="AK19" s="6"/>
+    </row>
+    <row r="20" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD20" s="5"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
+      <c r="AG20" s="6"/>
+      <c r="AH20" s="6"/>
+      <c r="AI20" s="6"/>
+      <c r="AJ20" s="6"/>
+      <c r="AK20" s="6"/>
+    </row>
+    <row r="21" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD21" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD22" s="1"/>
-    </row>
-    <row r="23" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD23" s="1" t="s">
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="6"/>
+      <c r="AG21" s="6"/>
+      <c r="AH21" s="6"/>
+      <c r="AI21" s="6"/>
+      <c r="AJ21" s="6"/>
+      <c r="AK21" s="6"/>
+    </row>
+    <row r="22" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD22" s="5"/>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
+      <c r="AG22" s="6"/>
+      <c r="AH22" s="6"/>
+      <c r="AI22" s="6"/>
+      <c r="AJ22" s="6"/>
+      <c r="AK22" s="6"/>
+    </row>
+    <row r="23" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD23" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD24" s="1"/>
-    </row>
-    <row r="25" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD25" s="1" t="s">
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6"/>
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="6"/>
+      <c r="AJ23" s="6"/>
+      <c r="AK23" s="6"/>
+    </row>
+    <row r="24" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD24" s="5"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="6"/>
+      <c r="AI24" s="6"/>
+      <c r="AJ24" s="6"/>
+      <c r="AK24" s="6"/>
+    </row>
+    <row r="25" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD25" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD26" s="1" t="s">
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
+      <c r="AG25" s="6"/>
+      <c r="AH25" s="6"/>
+      <c r="AI25" s="6"/>
+      <c r="AJ25" s="6"/>
+      <c r="AK25" s="6"/>
+    </row>
+    <row r="26" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD26" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD27" s="1" t="s">
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="6"/>
+      <c r="AI26" s="6"/>
+      <c r="AJ26" s="6"/>
+      <c r="AK26" s="6"/>
+    </row>
+    <row r="27" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD27" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD28" s="1" t="s">
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="6"/>
+      <c r="AG27" s="6"/>
+      <c r="AH27" s="6"/>
+      <c r="AI27" s="6"/>
+      <c r="AJ27" s="6"/>
+      <c r="AK27" s="6"/>
+    </row>
+    <row r="28" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD28" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD29" s="1" t="s">
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="6"/>
+      <c r="AG28" s="6"/>
+      <c r="AH28" s="6"/>
+      <c r="AI28" s="6"/>
+      <c r="AJ28" s="6"/>
+      <c r="AK28" s="6"/>
+    </row>
+    <row r="29" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD29" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="30" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD30" s="1" t="s">
+      <c r="AE29" s="6"/>
+      <c r="AF29" s="6"/>
+      <c r="AG29" s="6"/>
+      <c r="AH29" s="6"/>
+      <c r="AI29" s="6"/>
+      <c r="AJ29" s="6"/>
+      <c r="AK29" s="6"/>
+    </row>
+    <row r="30" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD30" s="5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD31" s="1" t="s">
+      <c r="AE30" s="6"/>
+      <c r="AF30" s="6"/>
+      <c r="AG30" s="6"/>
+      <c r="AH30" s="6"/>
+      <c r="AI30" s="6"/>
+      <c r="AJ30" s="6"/>
+      <c r="AK30" s="6"/>
+    </row>
+    <row r="31" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD31" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD32" s="1" t="s">
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6"/>
+      <c r="AG31" s="6"/>
+      <c r="AH31" s="6"/>
+      <c r="AI31" s="6"/>
+      <c r="AJ31" s="6"/>
+      <c r="AK31" s="6"/>
+    </row>
+    <row r="32" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD32" s="5" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="33" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD33" s="1" t="s">
+      <c r="AE32" s="6"/>
+      <c r="AF32" s="6"/>
+      <c r="AG32" s="6"/>
+      <c r="AH32" s="6"/>
+      <c r="AI32" s="6"/>
+      <c r="AJ32" s="6"/>
+      <c r="AK32" s="6"/>
+    </row>
+    <row r="33" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD33" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="30:30" x14ac:dyDescent="0.2">
-      <c r="AD34" s="1" t="s">
+      <c r="AE33" s="6"/>
+      <c r="AF33" s="6"/>
+      <c r="AG33" s="6"/>
+      <c r="AH33" s="6"/>
+      <c r="AI33" s="6"/>
+      <c r="AJ33" s="6"/>
+      <c r="AK33" s="6"/>
+    </row>
+    <row r="34" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD34" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="63" spans="2:9" s="2" customFormat="1" ht="27.75" x14ac:dyDescent="0.4">
-      <c r="B63" s="3" t="s">
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6"/>
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="6"/>
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="6"/>
+    </row>
+    <row r="35" spans="30:37" x14ac:dyDescent="0.2">
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="6"/>
+      <c r="AF35" s="6"/>
+      <c r="AG35" s="6"/>
+      <c r="AH35" s="6"/>
+      <c r="AI35" s="6"/>
+      <c r="AJ35" s="6"/>
+      <c r="AK35" s="6"/>
+    </row>
+    <row r="63" spans="2:9" s="1" customFormat="1" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="B63" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1347,58 +1588,58 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:27" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
     </row>
     <row r="3" spans="2:27" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="5"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1414,28 +1655,28 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:21" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/AI使用记录.xlsx
+++ b/AI使用记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\testdemo\java-demo\fastApi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23C2293-BD04-4A42-B9D6-993C382B2C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADBD7F3-9E9C-4D05-9301-DB3A41D50D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1、项目起步过程" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>自动化测试过程中解决状态响应错误问题</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -141,6 +141,10 @@
   </si>
   <si>
     <t>且在安装Docker for Windows和HyperV的过程中均涉及到电脑重启的过程，为了规避风险所以CI/CD的过程仅尝试到书写完Dockerfile</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用大模型完成每一个变动的github方便上传</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -842,6 +846,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>591740</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>19123</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF266731-39A3-4C9D-A561-654D19198E5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="11293929"/>
+          <a:ext cx="18281026" cy="10278909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1651,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64195C3-9EB0-4EC9-B950-EC7F8595194A}">
-  <dimension ref="B2:U2"/>
+  <dimension ref="B2:U63"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:21" ht="25.5" x14ac:dyDescent="0.35">
@@ -1678,6 +1726,30 @@
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
     </row>
+    <row r="63" spans="2:21" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="B63" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="2"/>
+      <c r="U63" s="2"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AI使用记录.xlsx
+++ b/AI使用记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\testdemo\java-demo\fastApi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADBD7F3-9E9C-4D05-9301-DB3A41D50D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AAD27D-0CCF-4E70-B638-1F789224FEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1、项目起步过程" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="3、自动化接口测试过程" sheetId="1" r:id="rId3"/>
     <sheet name="4、CICD" sheetId="4" r:id="rId4"/>
     <sheet name="5、总结" sheetId="5" r:id="rId5"/>
+    <sheet name="6、提升" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>自动化测试过程中解决状态响应错误问题</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -108,9 +109,6 @@
     <t>|-------|------|-------|------|</t>
   </si>
   <si>
-    <t>| test_user | test_password123 | 13800138004 | 基础测试用户（fixture创建） |</t>
-  </si>
-  <si>
     <t>| new_user | pass123 | 13800138000 | 注册成功测试 |</t>
   </si>
   <si>
@@ -145,6 +143,14 @@
   </si>
   <si>
     <t>利用大模型完成每一个变动的github方便上传</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>| test_user | test_password123 | 13800138004 | 基础测试用户（fixture创建） |</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用大模型完成项目的前端页面</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -890,6 +896,99 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>591740</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>150317</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48A8F73D-5A07-4B5D-BF4E-A9F581941BF3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="21880286"/>
+          <a:ext cx="18281026" cy="4572638"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>450226</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>144309</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{606F1796-FD4A-41D8-BC1A-82B074624616}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="180975"/>
+          <a:ext cx="18281026" cy="10278909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1506,7 +1605,7 @@
     </row>
     <row r="27" spans="30:37" x14ac:dyDescent="0.2">
       <c r="AD27" s="5" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="AE27" s="6"/>
       <c r="AF27" s="6"/>
@@ -1518,7 +1617,7 @@
     </row>
     <row r="28" spans="30:37" x14ac:dyDescent="0.2">
       <c r="AD28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE28" s="6"/>
       <c r="AF28" s="6"/>
@@ -1530,7 +1629,7 @@
     </row>
     <row r="29" spans="30:37" x14ac:dyDescent="0.2">
       <c r="AD29" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE29" s="6"/>
       <c r="AF29" s="6"/>
@@ -1542,7 +1641,7 @@
     </row>
     <row r="30" spans="30:37" x14ac:dyDescent="0.2">
       <c r="AD30" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE30" s="6"/>
       <c r="AF30" s="6"/>
@@ -1554,7 +1653,7 @@
     </row>
     <row r="31" spans="30:37" x14ac:dyDescent="0.2">
       <c r="AD31" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE31" s="6"/>
       <c r="AF31" s="6"/>
@@ -1566,7 +1665,7 @@
     </row>
     <row r="32" spans="30:37" x14ac:dyDescent="0.2">
       <c r="AD32" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE32" s="6"/>
       <c r="AF32" s="6"/>
@@ -1578,7 +1677,7 @@
     </row>
     <row r="33" spans="30:37" x14ac:dyDescent="0.2">
       <c r="AD33" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE33" s="6"/>
       <c r="AF33" s="6"/>
@@ -1590,7 +1689,7 @@
     </row>
     <row r="34" spans="30:37" x14ac:dyDescent="0.2">
       <c r="AD34" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AE34" s="6"/>
       <c r="AF34" s="6"/>
@@ -1637,7 +1736,7 @@
   <sheetData>
     <row r="2" spans="2:27" ht="25.5" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1661,7 +1760,7 @@
     </row>
     <row r="3" spans="2:27" ht="25.5" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -1704,7 +1803,7 @@
   <sheetData>
     <row r="2" spans="2:21" ht="25.5" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1728,7 +1827,7 @@
     </row>
     <row r="63" spans="2:21" ht="25.5" x14ac:dyDescent="0.35">
       <c r="B63" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -1756,4 +1855,40 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C735D89-2793-4429-B868-B842A3E17F67}">
+  <dimension ref="B2:U2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="2:21" ht="25.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/AI使用记录.xlsx
+++ b/AI使用记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\testdemo\java-demo\fastApi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AAD27D-0CCF-4E70-B638-1F789224FEA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70CA6E2-4901-461A-940F-07D2F84F7526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1、项目起步过程" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,26 @@
     <sheet name="5、总结" sheetId="5" r:id="rId5"/>
     <sheet name="6、提升" sheetId="7" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>自动化测试过程中解决状态响应错误问题</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -151,6 +160,14 @@
   </si>
   <si>
     <t>利用大模型完成项目的前端页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通用户账号: test_user / password123</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理员账号: admin / admin_password123</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -158,7 +175,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,6 +230,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -254,7 +280,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
@@ -262,6 +288,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -955,7 +982,7 @@
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>450226</xdr:colOff>
-      <xdr:row>58</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>144309</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -980,6 +1007,50 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="685800" y="180975"/>
+          <a:ext cx="18281026" cy="10278909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>591740</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>19124</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{622FB2D9-646F-421F-AEC9-9D7B00FB1761}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="10763250"/>
           <a:ext cx="18281026" cy="10278909"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1859,10 +1930,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C735D89-2793-4429-B868-B842A3E17F67}">
-  <dimension ref="B2:U2"/>
+  <dimension ref="B2:AC4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="29" max="29" width="40" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:29" ht="25.5" x14ac:dyDescent="0.35">
       <c r="B2" s="2" t="s">
         <v>36</v>
       </c>
@@ -1886,9 +1960,20 @@
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
     </row>
+    <row r="3" spans="2:29" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="AC3" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="2:29" ht="27.75" x14ac:dyDescent="0.4">
+      <c r="AC4" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/AI使用记录.xlsx
+++ b/AI使用记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\testdemo\java-demo\fastApi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70CA6E2-4901-461A-940F-07D2F84F7526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD7A688-2BC9-448D-86B5-63BD7F151D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1、项目起步过程" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>自动化测试过程中解决状态响应错误问题</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -168,6 +168,10 @@
   </si>
   <si>
     <t>管理员账号: admin / admin_password123</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手动测试过程</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -728,6 +732,94 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="680357" y="11144250"/>
+          <a:ext cx="18281026" cy="10278909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>591740</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>19124</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B3AB8A1-CA79-4B94-8D85-6D347D170C1A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="22261286"/>
+          <a:ext cx="18281026" cy="10278909"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>184</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>591740</xdr:colOff>
+      <xdr:row>242</xdr:row>
+      <xdr:rowOff>19123</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76A27A91-E46B-4561-B7F7-CC9B2B95B03A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="680357" y="32874857"/>
           <a:ext cx="18281026" cy="10278909"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1382,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:AK63"/>
+  <dimension ref="B2:AK124"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:37" ht="25.5" x14ac:dyDescent="0.35">
@@ -1791,6 +1883,11 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B124" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
